--- a/www/download/COUNTRY.USA.zdW16.xlsx
+++ b/www/download/COUNTRY.USA.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.667</t>
+          <t>0.999999998943296</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.773</t>
+          <t>0.999999999121932</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.805</t>
+          <t>1.00000000102884</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2.905</t>
+          <t>0.999999997105902</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>3.146</t>
+          <t>0.999999997871972</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>3.427</t>
+          <t>0.999999996015961</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>3.758</t>
+          <t>1.0000000024428</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>4.087</t>
+          <t>1.00000000051001</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>4.371</t>
+          <t>1.00000000299519</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>4.427</t>
+          <t>1.00000000010837</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>1.00000000221065</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>4.897</t>
+          <t>0.99999999954881</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>5.008</t>
+          <t>0.999999996664542</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>5.138</t>
+          <t>1.00000000109963</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.99999999925092</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>150.433</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>150.399</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>149.192</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>148.589</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>150.048</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>155.009</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>155.569</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>154.696</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>147.906</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>146.533</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>147.899</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>150.631</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>152.958</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>155.77</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>139.709</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>139.748</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>138.781</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>137.829</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>139.223</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>141.123</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>144.012</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>144.797</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>144.175</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>137.692</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>136.526</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>138.029</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>140.695</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>143.158</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>145.951</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>267851.122</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>266794.928</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>263860.736</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>261972.505</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>264921.645</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>269187.999</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>274200.86</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>275901.354</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>274104.683</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>260237.659</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>260971.169</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>264895.492</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>269975.963</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>274801.011</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>280476.1</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>248493.695</t>
+          <t>236343039397.868</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>247634.371</t>
+          <t>221130435504.106</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>245209.02</t>
+          <t>218729419087.842</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>242844.555</t>
+          <t>220590295633.016</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>245677.374</t>
+          <t>229464213930.877</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>249806.48</t>
+          <t>237789903464.14</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>254542.763</t>
+          <t>241527998662.097</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>256427.007</t>
+          <t>229169505089.862</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>255070.419</t>
+          <t>225043369249.361</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>241928.353</t>
+          <t>188367314993.018</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>242827.728</t>
+          <t>191579887546.213</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>247004.674</t>
+          <t>208573217449.159</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>252068.151</t>
+          <t>210869522806.899</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>257055.775</t>
+          <t>211295199862.33</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>262614.229</t>
+          <t>217618111854.757</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>141224321150.187</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>144670333162.606</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>148697637461.773</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>151688098675.757</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>154523640989.314</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>157071849972.081</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>154784067402.218</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>144232731969.459</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>134113184025.187</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>122138153171.296</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>118287849803.04</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>119712743528.617</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>122268490836.398</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>122033401386.493</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>124594626817.757</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1166145.75597938</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1110614.05462719</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1124606.75348054</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1067486.49415398</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1033005.92103036</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>970946.976903646</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>911011.152191785</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>799278.399666224</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>754662.680201411</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>727961.432532037</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>679653.273648092</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>679541.257237775</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>642815.361836739</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>629688.542830263</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>616200.476052389</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>849544.215841984</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>826357.30071013</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>814189.909328612</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>877187.031439594</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>978586.729084624</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1073833.28847318</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1165021.8294978</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1324133.51566718</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>1425340.34746237</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1213035.33983782</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1338494.67658668</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1448109.77783564</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1445105.23553206</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>1462947.73309519</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1507400.50281754</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2143948.01719641</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1976576.76031316</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1969496.53211236</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2162433.79250834</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2478911.40757932</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2774576.64092702</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2978018.39856208</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>3169712.11544808</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>3394840.47807374</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2596900.38616335</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2918057.21326584</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>3387274.88706144</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>3345168.81588278</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>3332486.01248535</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>3444191.09483201</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.759567282576884</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.711714942424758</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.64904449179993</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.600946660417283</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.589901534982531</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.590396242511964</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.644502352677883</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.777869721377101</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.901904133094757</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.980776249831617</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1.05285435828218</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1.06331144637876</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1.06159534051403</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1.1064378447166</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1.10774923210872</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.999999998943296</t>
+          <t>1010.84829315011</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.999999999121932</t>
+          <t>1035.22233863841</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.00000000102884</t>
+          <t>1071.45342784707</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.999999997105902</t>
+          <t>1100.55336040435</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.999999997871972</t>
+          <t>1109.89886790766</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.999999996015961</t>
+          <t>1113.01160842541</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1.0000000024428</t>
+          <t>1074.80217109762</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.00000000051001</t>
+          <t>996.102675994786</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.00000000299519</t>
+          <t>930.21007790674</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.00000000010837</t>
+          <t>887.04072349989</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.00000000221065</t>
+          <t>866.415028451256</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.99999999954881</t>
+          <t>867.299485882478</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.999999996664542</t>
+          <t>869.034067098913</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>1.00000000109963</t>
+          <t>852.436906803387</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.99999999925092</t>
+          <t>853.675145838168</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5.863</t>
+          <t>116951500228.61</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>6.054</t>
+          <t>117707196055.213</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>121655492144.241</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>6.373</t>
+          <t>125814824407.865</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>6.749</t>
+          <t>130838876763.083</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>7.098</t>
+          <t>133903622749.779</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>7.514</t>
+          <t>133939732259.433</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>7.909</t>
+          <t>128011107264.38</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>118817494156.146</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>7.796</t>
+          <t>113869921874.007</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>7.969</t>
+          <t>111311911344.605</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>8.277</t>
+          <t>115644786578.361</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>8.619</t>
+          <t>116688299128.464</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>8.849</t>
+          <t>116702872592.883</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>9.258</t>
+          <t>119169304401.208</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6.215</t>
+          <t>104897841832.301</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>6.423</t>
+          <t>106093143529.126</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>110048413156.34</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>6.772</t>
+          <t>114123471536.657</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>7.167</t>
+          <t>117900627391.454</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>7.539</t>
+          <t>120265235228.156</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>7.986</t>
+          <t>119840694043.566</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>8.369</t>
+          <t>113075994036.134</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>104952402514.384</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>100367747249.657</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>8.417</t>
+          <t>96742163007.8562</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>8.74</t>
+          <t>99127346014.7803</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>98815002690.7896</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>9.349</t>
+          <t>97799648137.4018</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>9.771</t>
+          <t>99146507233.1868</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>27.927</t>
+          <t>12053658396.3088</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>29.491</t>
+          <t>11614052526.0875</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>30.943</t>
+          <t>11607078987.9004</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>32.646</t>
+          <t>11691352871.2087</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>35.988</t>
+          <t>12938249371.6293</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>39.63</t>
+          <t>13638387521.6233</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>42.855</t>
+          <t>14099038215.8666</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>44.747</t>
+          <t>14935113228.2454</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>46.192</t>
+          <t>13865091641.762</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>45.273</t>
+          <t>13502174624.3501</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>46.192</t>
+          <t>14569748336.7489</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>47.651</t>
+          <t>16517440563.5809</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>49.154</t>
+          <t>17873296437.6746</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>51.528</t>
+          <t>18903224455.481</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>53.547</t>
+          <t>20022797168.0217</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>18.565</t>
+          <t>1778.65558427563</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>18.863</t>
+          <t>1772.00554577927</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>19.175</t>
+          <t>1766.87437341136</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>20.135</t>
+          <t>1761.92722695037</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>21.697</t>
+          <t>1764.62991376177</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>23.515</t>
+          <t>1770.12947991196</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>24.888</t>
+          <t>1767.51469903334</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>26.151</t>
+          <t>1770.94078703384</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>26.826</t>
+          <t>1769.17039181723</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>24.657</t>
+          <t>1757.02919774204</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>26.094</t>
+          <t>1778.62386723734</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>27.536</t>
+          <t>1789.50895665973</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>28.663</t>
+          <t>1791.59658347908</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>29.572</t>
+          <t>1795.60536072381</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>30.971</t>
+          <t>1799.3331331107</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>10.285</t>
+          <t>1780.53018104335</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10.622</t>
+          <t>1773.91235709432</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>10.978</t>
+          <t>1768.59667174399</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>11.511</t>
+          <t>1763.06478843495</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>12.275</t>
+          <t>1765.57704158293</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>13.094</t>
+          <t>1770.97808085155</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>13.856</t>
+          <t>1768.93912399701</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>14.478</t>
+          <t>1773.50395676626</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>14.719</t>
+          <t>1771.89049163513</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>14.419</t>
+          <t>1759.47669265784</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>14.964</t>
+          <t>1780.96671663388</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>15.518</t>
+          <t>1791.06102532023</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>16.155</t>
+          <t>1792.2998444773</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>16.663</t>
+          <t>1796.57724591493</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>17.348</t>
+          <t>1800.57310107365</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>926537.752225788</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>870631.004014701</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>851308.036736769</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>885122.052969931</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>998945.634376492</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>1103626.03982345</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1262071.65873159</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>1429140.7920663</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>1579602.18534601</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1340079.62190304</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1552492.19842277</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1767450.39663382</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1832362.09747885</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>1866768.4829331</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>1927091.4918161</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>18192554026.7876</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>16132694019.0047</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>15175301664.9811</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>15006722932.5523</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>16028276420.8762</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>16850752766.6525</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>18685033512.9131</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>18818791473.3689</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>20186200214.4901</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>15671752830.8446</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>17318063097.3423</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>20305912042.7207</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>20519250070.2232</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>20281153250.1621</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>20520058784.2879</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>1286230.04532767</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1215834.42780198</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1246620.71558412</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1345765.2702561</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1556082.64647089</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>1753836.92695339</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>1954383.73651244</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2065109.44455472</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2210612.12258807</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1676255.39194309</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>2011649.42781054</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>2287828.42638923</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>2328276.8390288</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2333411.78570173</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2407668.02758544</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>267851.122</t>
+          <t>184333734149.269</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>266794.928</t>
+          <t>182972995362.433</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>263860.736</t>
+          <t>193450850651.762</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>261972.505</t>
+          <t>203012880684.957</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>264921.645</t>
+          <t>215408286692.208</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>269187.999</t>
+          <t>223304365508.88</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>274200.86</t>
+          <t>222730945682.407</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>275901.354</t>
+          <t>202051971526.964</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>274104.683</t>
+          <t>186839800906.078</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>260237.659</t>
+          <t>158167616709.209</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>260971.169</t>
+          <t>163483453597.752</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>264895.492</t>
+          <t>173345466917.09</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>269975.963</t>
+          <t>173081769481.829</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>274801.011</t>
+          <t>171077338204.593</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>280476.1</t>
+          <t>174463434066.743</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>248493.695</t>
+          <t>-359692.293101885</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>247634.371</t>
+          <t>-345203.423787277</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>245209.02</t>
+          <t>-395312.678847355</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>242844.555</t>
+          <t>-460643.217286168</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>245677.374</t>
+          <t>-557137.012094403</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>249806.48</t>
+          <t>-650210.887129935</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>254542.763</t>
+          <t>-692312.077780843</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>256427.007</t>
+          <t>-635968.652488418</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>255070.419</t>
+          <t>-631009.93724206</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>241928.353</t>
+          <t>-336175.770040049</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>242827.728</t>
+          <t>-459157.229387768</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>247004.674</t>
+          <t>-520378.029755408</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>252068.151</t>
+          <t>-495914.74154995</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>257055.775</t>
+          <t>-466643.302768626</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>262614.229</t>
+          <t>-480576.535769342</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>279819.374</t>
+          <t>-166141180122.482</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>263033.544</t>
+          <t>-166840301343.428</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>261346.943</t>
+          <t>-178275548986.781</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>263265.32</t>
+          <t>-188006157752.404</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>274623.781</t>
+          <t>-199380010271.332</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>287294.928</t>
+          <t>-206453612742.227</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>292910.514</t>
+          <t>-204045912169.494</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>279152.76</t>
+          <t>-183233180053.595</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>276124.958</t>
+          <t>-166653600691.588</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>232119.324</t>
+          <t>-142495863878.365</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>238036.544</t>
+          <t>-146165390500.41</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>259656.313</t>
+          <t>-153039554874.37</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>261581.919</t>
+          <t>-152562519411.606</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>256878.437</t>
+          <t>-150796184954.431</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>217618.112</t>
+          <t>-153943375282.455</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2.274</t>
+          <t>3340872.49839961</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2.117</t>
+          <t>3363495.99601206</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2.116</t>
+          <t>3400260.77886808</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>3612441.90735317</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2.675</t>
+          <t>3909926.59092002</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>3.005</t>
+          <t>4162662.20274867</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>3.237</t>
+          <t>4468531.61926718</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>3.483</t>
+          <t>4658055.19074406</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>3.739</t>
+          <t>4742562.90156793</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2.861</t>
+          <t>4515917.63075964</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>4725728.18791814</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>3.764</t>
+          <t>4966989.20102943</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>3.695</t>
+          <t>5137956.35125637</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>3.626</t>
+          <t>5343614.49196028</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>3.444</t>
+          <t>5539113.04878383</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>93651.46</t>
+          <t>0.14572401928332</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>92449.104</t>
+          <t>0.142371622330331</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>90422.747</t>
+          <t>0.1440661828289</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>89482.021</t>
+          <t>0.145150753774315</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>90584.373</t>
+          <t>0.141938198166369</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>92030.874</t>
+          <t>0.140163012359585</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>94487.459</t>
+          <t>0.136980828727646</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>95734.569</t>
+          <t>0.136514449273692</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>94485.557</t>
+          <t>0.133751316124366</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>87988.053</t>
+          <t>0.136247780640749</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>87876.502</t>
+          <t>0.141734440710953</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>89168.115</t>
+          <t>0.142238461515611</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>91095.149</t>
+          <t>0.143117007877806</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>92757.729</t>
+          <t>0.141940555263508</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>95243.743</t>
+          <t>0.141497602813533</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.761</t>
+          <t>5863150.00112362</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.744</t>
+          <t>6053753.00712748</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.732</t>
+          <t>6149709.00391068</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.788</t>
+          <t>6372707.99557373</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.882</t>
+          <t>6748782.00020607</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.963</t>
+          <t>7097916.00512548</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.044</t>
+          <t>7513699.0060963</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.194</t>
+          <t>7908768.99987201</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.279</t>
+          <t>8089961.98729939</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.084</t>
+          <t>7795659.99561757</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>7969484.99978942</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1.293</t>
+          <t>8277114.98791631</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1.287</t>
+          <t>8618539.00241532</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>1.309</t>
+          <t>8848749.99499199</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>1.507</t>
+          <t>9258365.00016341</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>159922.399</t>
+          <t>6215147.80314446</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>163183.912</t>
+          <t>6423146.43420744</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>168288.379</t>
+          <t>6519691.34384195</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>171437.537</t>
+          <t>6772090.25714787</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>174461.439</t>
+          <t>7166902.59873644</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>178350.677</t>
+          <t>7539079.37444122</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>176717.382</t>
+          <t>7985511.94723064</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>164294.24</t>
+          <t>8369068.73031058</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>153797.292</t>
+          <t>8540298.39291486</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>140905.354</t>
+          <t>8250330.92288482</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>136682.053</t>
+          <t>8417431.13619961</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>139060.172</t>
+          <t>8740156.61422045</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>141892.873</t>
+          <t>9120483.96233394</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>139721.128</t>
+          <t>9349299.15897539</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>124594.627</t>
+          <t>9771294.96707294</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>55.38</t>
+          <t>27926969.0053173</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>51.75</t>
+          <t>29490972.0495477</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>45.71</t>
+          <t>30942872.995062</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>32645919.0643944</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>35987652.0362497</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>40.06</t>
+          <t>39629875.0508333</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>44.04</t>
+          <t>42855464.9967933</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>56.08</t>
+          <t>44746686.9858048</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>65.85</t>
+          <t>46192289.9759759</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>45273493.9909204</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>77.66</t>
+          <t>46191595.0277175</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>77.62</t>
+          <t>47650756.9159532</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>77.65</t>
+          <t>49153970.1324136</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>83.98</t>
+          <t>51527646.9536609</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>110.77</t>
+          <t>53547021.0467933</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.379</t>
+          <t>7981469.79360341</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>8065308.08926517</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>8055440.85162016</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.274</t>
+          <t>8174110.78525825</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.234</t>
+          <t>8354350.56575899</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.169</t>
+          <t>8483791.70327951</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.102</t>
+          <t>8698184.91180531</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.969</t>
+          <t>8810353.04347093</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.919</t>
+          <t>8808827.56392697</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>8370881.05308909</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.842</t>
+          <t>8417431.13658108</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.845</t>
+          <t>8602702.50991984</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.802</t>
+          <t>8787559.20379157</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.768</t>
+          <t>8837457.81058245</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.616</t>
+          <t>9046200.33802274</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>7494616.00132738</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>7571980.85572906</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>7574943.25626301</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>7670635.21498004</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>7857097.90403499</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>7980728.53269528</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>8181105.44788374</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>8335521.37491411</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>8351755.50936486</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>7909611.19973774</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>7969485.00049775</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>8152436.22743455</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>8310886.45046043</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>8372016.23710383</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>8577938.91393237</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>4069630.16985554</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4198677.53479256</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>4457821.59815805</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>4738579.75985213</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>5108022.48626356</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>5554642.66655878</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>5870377.11076936</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>6108569.33068942</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>6178279.57908514</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>6168413.07811518</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>6546939.88680039</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>6777770.35377955</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>7034769.13066606</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>7313862.82002462</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>7576775.11592706</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>248493695000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>247634371000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>245209020000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>242844555000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>245677374000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>249806480000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>254542763000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>256427007000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>255070419000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>241928353000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>242827728000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>247004674000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>252068151000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>257055775000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>262614229000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>267851121690.988</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>266794928420.605</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>263860736403.136</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>261972504587.059</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>264921644691.804</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>269187998859.722</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>274200860236.142</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>275901353845.2</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>274104683346.715</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>260237659395.632</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>260971168828.067</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>264895491592.929</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>269975962680.956</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>274801011496.567</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>280476100217.87</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>93651460046.8406</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>92449103650.838</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>90422746621.2516</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>89482021258.212</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>90584372586.2988</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>92030874273.2381</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>94487458845.8295</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>95734568757.6579</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>94485557183.5265</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>87988053440.3063</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>87876501686.0968</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>89168114680.1731</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>91095148913.1289</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>92757728762.9651</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>95243742928.2836</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>150433351</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>150399160</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>149192148</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>148589267</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>150048193</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>151999622</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>155008647</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>155568502</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>154696176</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>147906284</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>146533434</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>147898641</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>150631025</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>152958083</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>155770460</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>139708720</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>139748079</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>138781242</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>137828936</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>139223172</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>141123281</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>144011681</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>144797053</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>144175157</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>137691709</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>136525621</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>138029303</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>140694704</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>143158280</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>145950866</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>267851121690.988</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>266794928420.605</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>263860736403.136</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>261972504587.059</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>264921644691.804</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>269187998859.722</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>274200860236.142</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>275901353845.2</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>274104683346.715</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>260237659395.632</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>260971168828.067</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>264895491592.929</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>269975962680.956</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>274801011496.567</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>280476100217.87</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>248493695000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>247634371000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>245209020000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>242844555000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>245677374000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>249806480000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>254542763000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>256427007000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>255070419000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>241928353000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>242827728000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>247004674000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>252068151000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>257055775000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>262614229000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>18564550</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>18863118</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>19175007</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>20135087</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>21697287</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>23514906</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>24887955</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>26151311</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>26825683</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>24657234</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>26093505</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>27535973</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>28663254</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>29571550</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>30971023</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>10284778</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10621824</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>10977513</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>11510670</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>12274925</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>13093722</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>13855889</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>14477638</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>14718578</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>14418744</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>14964371</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>15517927</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>16155253</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>16663162</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>17348070</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>36487274.7317481</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>37497262.9985287</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>38758422.8913328</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>39321461.7922774</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>41720353.2987346</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>43992090.765024</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>45906171.2884217</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>46571150.5356126</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>46314423.0913304</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>46253505.2929523</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>46191595.0704148</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>46436008.096009</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>47300877.5572663</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>48649776.309108</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>49538830.4005774</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
